--- a/delhi_leads_clean.xlsx
+++ b/delhi_leads_clean.xlsx
@@ -34,12 +34,48 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9DAF8"/>
+        <bgColor rgb="00C9DAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -65,11 +101,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,20 +477,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,268 +517,2296 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Maps URL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Competitor Name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Competitor Website</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cottage cafe by La Polo</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>46, Tolstoy Rd, Atul Grove Road, Connaught Place, New Delhi, Delhi 110001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Connaught Place</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>081302 14666</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Dwarka Heights</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>F-692, block-H, Palam Extension, Palam, Ramphal Chowk Rd, Sector 7 Dwarka, Dwarka, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>011 6136 4449</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Coffee Club Cafe</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>C-305, Palam Extension Sector 7, Dwarka, Ramphal Chowk Rd, near MiniSo, opp. Vishal Mega Mart Lane, Area, New Delhi, Delhi 110075</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>098118 18053</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>DownTown Cafe</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>H3PC+WMR, Block G, Sector 7 Dwarka, Dwarka, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>070602 42618</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>The nukkad cafe</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>C-924 palam extension, Ramphal Chowk Rd, Block C, Sector 7 Dwarka, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>096439 69168</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Olives 51</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Ramphal Chowk, E-1089, Block E, Sector 7 Dwarka, Dwarka, New Delhi, Delhi, 110075</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>080105 73627</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-olives-51-palam-dwarka2-delhi-35261/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Sardar+Saab+Cafe+%7C+Hauz+Khaz/@28.6517105,76.9748118,12z/data=!3m1!5s0x390ce20d0fe82687:0x2b85af776090ae13!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce36e118dba61:0x10f65126e31940e1!8m2!3d28.5504659!4d77.2044369!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11f61pp6_6?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Ten</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Plot 13, Odeon Plaza 2, Shop 109, 1st Floor, above Citi Bank Atm, Sector 10 Dwarka, Dwarka, New Delhi, Delhi 110075</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>093117 61176</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-ten-dwarka-delhi-322264/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Cafe+Ten/@28.5836629,76.9347208,12z/data=!3m1!5s0x390d1b206106fca1:0x9d4e494ec51387f8!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d1b343e1da4b5:0x17f386cf8aaf73f1!8m2!3d28.5905942!4d77.0575952!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11qld_w2f5?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Cafe YNM</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A-2, MAIN PALAM DABRI ROAD, MAHAVIR ENCLAVE, PALAM, Dwarka, New Delhi, Delhi 110045</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>088514 29306</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-ynm-mahavir-enclave-dwarka-koramangala-delhi-1042208/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Dose Cafe</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SHOP AT PLOT A1/1, BLK A1, AMAR SINGH GAHLOT CHOWK, Dwarka Mor, Block B, Sewak Park, Dwarka, New Delhi, Delhi, 110059</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Dwarka</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>090132 83706</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>https://link.zomato.com/xqzv/rshare?id=11286629130563f66</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Brew Cafe</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>230</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>E18, Market Ln, Hauz Khas Market, Block E, Hauz Khas, New Delhi, Delhi 110016</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Hauz Khas</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>085888 21888</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Cafe</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Brew+Cafe/@28.5512747,77.1988559,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390ce212bd155555:0xf4d375294335861d!8m2!3d28.5512747!4d77.2083831!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEEY2FmZeABAA!16s%2Fg%2F11f1r8qrrm?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>[HIGH] High</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>ShellBeacon Cafe, Bar &amp; Kitchen</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>http://www.shellbeacon.com/</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Lakeview bistro</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>879</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>12b, Hauz Khas Fort Rd, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Hauz Khas</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>099106 00123</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Restaurant</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Lakeview+bistro/@28.5535955,77.1846895,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390ce3002eb45c95:0x48355ab98ee4ea4e!8m2!3d28.5539077!4d77.194598!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEKcmVzdGF1cmFudOABAA!16s%2Fg%2F11xdvsjnsb?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>[HIGH] High</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Recycle Cafe</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>160</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>50A 2nd Floor, Hauz Khas Fort Rd, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Hauz Khas</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>098731 19688</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Live music bar</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Recycle+Cafe/@28.5535955,77.1846895,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d5bff6bea75:0x39c545c9b829eaf!8m2!3d28.5535566!4d77.1941963!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEObGl2ZV9tdXNpY19iYXLgAQA!16s%2Fg%2F11gjkjcvqy?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>[HIGH] High</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Gypsy Café</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>818</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>13 a /ground floor / lakeside, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Hauz Khas</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>099905 05529</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>https://www.swiggy.com/restaurants/gypsy-cafe-hauz-khas-vikaspuri-delhi-678381/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Cafe</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Gypsy+Caf%C3%A9/@28.5544717,77.1846342,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d8a843af0fb:0x8fe97d6dd9444d5a!8m2!3d28.5544138!4d77.1940607!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEEY2FmZeABAA!16s%2Fg%2F11gbx9wm_p?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[MEDIUM] Medium</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>ShellBeacon Cafe, Bar &amp; Kitchen</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>http://www.shellbeacon.com/</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Tan Coffee | Hauz Khas, Delhi</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>385</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Shop No 8 &amp; 9, Surya Mansion, 1, Chaudhary Dilip Singh Marg, Kaushalya Park, Padmini Enclave, Hauz Khas, New Delhi, Delhi 110016</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hauz Khas</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>091666 63389</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>https://www.instagram.com/tancoffeeindia/</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Coffee shop</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Tan+Coffee+%7C+Hauz+Khas,+Delhi/@28.5530484,77.1982965,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390ce36d29b7767b:0xcb1f60e473a3a07d!8m2!3d28.5505264!4d77.2045074!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgELY29mZmVlX3Nob3DgAQA!16s%2Fg%2F11shwprtbf?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[MEDIUM] Medium</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Brucha coffee</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>B 14, DDA MARKET, BB Block, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>096252 96969</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>http://www.kofeynoe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Cafe b1</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Rajendra Arihant Tower, Dharam Marg, b1, B1 Market, Pocket B 1, Super Bazar, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>098718 94877</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>http://www.kofeynoe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Deja bru cafe</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Ganesh Nagar, Shivaji Marg, B2A Block, Block B 2B, Janakpuri, New Delhi, Delhi 110058</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>070420 89484</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Deja+bru+cafe/@28.6209996,76.9287952,12z/data=!4m10!1m2!2m1!1scafes+in+Delhi!3m6!1s0x390d0509124768f9:0xbe6f4d5620a31e20!8m2!3d28.633734!4d77.0902051!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBC2NvZmZlZV9zaG9w4AEA!16s%2Fg%2F11n07g9b8l?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Dolci Patisserie And Cafe</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>22, A3 Block Rd, Block A3, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>085878 88840</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Dolci+Patisserie+And+Cafe/@28.6209996,76.9287952,12z/data=!4m10!1m2!2m1!1scafes+in+Delhi!3m6!1s0x390d05eb9290aa9b:0xde35c536973546e3!8m2!3d28.6209996!4d77.0812305!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11l5tn2xj6?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>http://www.kofeynoe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Q Bistro Café and Patisserie</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Block C4, D/ 56-A, C4G, Block C4G, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>011 4370 1014</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Modern French restaurant</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Q+Bistro+Caf%C3%A9+and+Patisserie/@28.6422947,76.9539243,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d04bac3eb3275:0x19a8289004cb126c!8m2!3d28.6179699!4d77.0944172!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBGG1vZGVybl9mcmVuY2hfcmVzdGF1cmFudOABAA!16s%2Fg%2F11b7hrjq6m?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>WestSyd cafe</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Community Centre, B1-53, B1 Market, Pocket B 1, Super Bazar, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>011 3689 9658</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/WestSyd+cafe/@28.6301179,76.9382403,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d0567693d56b1:0x8185a4f926b7d348!8m2!3d28.6301179!4d77.0906756!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11x0cf0vg3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>IKVITI - Coffee Roasters &amp; Gourmet Kitchen</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>http://www.ikviti.coffee/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Cafe Stela</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Block B2B, Cafe Stela, 24/17, B1 Rd, Chhoti Subji Mandi, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Janakpuri</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>079821 90457</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cafe_stela?igshid=NzNkNDdiOGI=</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Cafe+Stela/@28.7081957,76.9520156,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d052960368037:0x9d712fef2f64c649!8m2!3d28.633834!4d77.0944652!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11s8k95h7h?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>ShellBeacon Cafe, Bar &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>http://www.shellbeacon.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Guliyano Cafe</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>863, Joshi Path, Block A, Karol Bagh, New Delhi, Delhi, 110005</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Karol Bagh</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>092125 08354</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.zomato.com/Guliyano2/menu</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Guliyano+Cafe/@28.5475066,77.0920603,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390cfd6388d11ccb:0x34b4e6c6fef08df!8m2!3d28.6532984!4d77.1998514!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11f1zlcd9z?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Cafe Veda</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Pardhan Chowk, RZ-169/A, Block C, Sadh Nagar, Palam, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>098056 55013</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cafe YNM</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>6, Palam Village Rd, Block RZ, Raj Nagar I, Raj Nagar, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>099113 44818</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>City Hot Cafe</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr"/>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Shop No A, 1/16, Metro Station, Dabri - Palam Rd, near by Dashrath Puri, Block B, Vijay Enclave, Mahavir Enclave, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>099904 56100</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Krishna Rooftop Cafe</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Top Floor, Tooti Chowk, 659, Main Bazar Rd, Bazar Sangatrashan, Main Bazar, Kaseru Walan, Paharganj, New Delhi, Delhi 110055</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>093102 73053</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Krishna+Rooftop+Cafe/@28.641161,77.0612152,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390cfd43e30e7cb5:0x7d91081ee8e8893d!8m2!3d28.641161!4d77.2136505!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F12q4x48x2?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Moonlight</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>on, DEEN DAYAL UPADHYAY HOSPITAL, C -Block, road, Hari Nagar, New Delhi, Delhi 110064</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>095400 07160</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Cafe West Delhi</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>http://www.cafewestdelhi.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Ninewatt coffee</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr"/>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Gopinath Bldg Rd, Gopi Nath Bazar, Delhi Cantonment, New Delhi, Delhi 110010</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>097100 03099</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Friendly Cafe</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr"/>
+      <c r="C30" s="7" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>gate no 1, K9 BK Dutt Colony, Jor Bagh, New Delhi, Delhi 110003</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>084472 41849</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Re Fuel Cafe</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr"/>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Old Mehrauli Rd, Block B, Raj Nagar I, Raj Nagar, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>099672 54230</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>The Flavour's Cafe</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>A-3/A, Gurudwara Rd, Mahavir Enclave I, Mahavir Enclave Part 1, Mahavir Enclave, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>088588 62921</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>The Study Cafe</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="7" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>First Floor, Hotel Neelgagan, Wz-80A, Mohan Nagar, Main, Pankha Rd, New Delhi, Delhi 110046</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>097110 29902</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Bites And Brew - Cafe and Diner (Vikaspuri)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>B, 50, Krishna Park Rd, Block-B, Shankar Garden, Vikaspuri, New Delhi, Delhi, 110018</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>095820 25050</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>https://zoma.to/r/19201577</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Cafe Trio</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Ram Chowk, RZ-150/1, Street Number 2, P Block, Sadh Nagar, Palam, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>096435 51414</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-trio-dwarka-delhi-1359117/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Josie's Coffee House</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Shop No. 3, Ground Floor, Central, beside La Pino's Pizza, Old Rajender Nagar market, Block 55, Rajinder Nagar, New Delhi, Delhi, 110060</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>096677 79071</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/josies-coffee-house-rajinder-nagar-karol-bagh-east-patel-nagar-delhi-375547/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Josie's+Coffee+House/@28.6301179,76.9382403,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d03295c656cab:0xc932eb8a70668def!8m2!3d28.6417586!4d77.1853622!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBCnJlc3RhdXJhbnTgAQA!16s%2Fg%2F11h_ftcn_b?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Mudra Cafe &amp; Lounge</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Metro Station, RZ-I/13, Main Rd, above Palam Dominos, near Palam, Palam Colony, Raj Nagar I, Palam, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>093105 69922</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/mudra-cafe-and-lounge-dwarka-delhi-998907/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Sehat Cafe</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>opposite Shiksha Bharti School Road, Block C, Palam Extension, Palam, New Delhi, Delhi, 110075</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>093191 24442</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/sehat-cafe-sector-7-dwarka2-delhi-76780/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Seven Seeds Coffee</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr"/>
+      <c r="C39" s="7" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>5, Block W, Arjun Nagar, Green Park, New Delhi, Delhi 110016</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>099718 66227</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/7-seeds-coffee-green-park-vikaspuri-delhi-928704/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Simpy's Cafe The Best family Restaurant</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr"/>
+      <c r="C40" s="7" t="inlineStr"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>CE 3 HARI NAGAR CLOCK TOWER, New Delhi, Delhi 110064</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>088516 09140</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/simpys-hari-nagar-koramangala-delhi-1351276/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Simpy's+Cafe+The+Best+family+Restaurant/@28.6422947,76.9539243,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d03369e1d6929:0x9d64a751a5092ff4!8m2!3d28.6253711!4d77.1110034!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11nnpp4g5k?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Cafe West Delhi</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>http://www.cafewestdelhi.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Soul Pantry - Andaz Delhi</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr"/>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Gate No. 5, Andaz Delhi, Asset, Street Number 1, Aerocity, New Delhi, Delhi 110037</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>085888 04222</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hyatt.com/andaz/delaz-andaz-delhi/dining</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Soul+Pantry+-+Andaz+Delhi/@28.6446478,76.9938964,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d1df00c45d56d:0xc58a108f30b8bea5!8m2!3d28.5537733!4d77.1223716!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11h6lp1vhl?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Tan Coffee | Prashant Vihar, Delhi</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr"/>
+      <c r="C42" s="7" t="inlineStr"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Block-B, Prashant Vihar, Sector 14, Rohini, New Delhi, Delhi, 110085</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>098211 09817</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tancoffeeindia/</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Tan+Coffee+%7C+Prashant+Vihar,+Delhi/@28.6446478,76.9938964,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d010004e97021:0x68758a07219f42ca!8m2!3d28.7108298!4d77.1331257!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBC2NvZmZlZV9zaG9w4AEA!16s%2Fg%2F11vk6lpll8?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>The BlackFox Cafe</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Shop No 2, DDA Market, Hari Enclave, Hari Nagar, New Delhi, Delhi, 110064</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>088601 99996</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/the-blackfox-cafe-hari-nagar-vikaspuri-delhi-740040/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Fast food restaurant</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Echoes</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>E-1, Major Sudesh Kumar Marg, Block E, Rajouri Garden, New Delhi, Delhi, 110027</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Rajouri Garden</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>087439 96500</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Echoes/@28.633734,76.9377698,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d0325c5ba6de3:0x6830a47ee35b0890!8m2!3d28.6421909!4d77.1238676!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11trrkwxp2?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Kartoon Cafe Rajouri Garden</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>J-2, 12, Block J, Rajouri Garden, New Delhi, Delhi, 110027</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Rajouri Garden</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>098736 61133</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Rajouri House Cafe &amp; Restro</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>above NYKAA Trends showroom, F-122, Highstreet, Main Market, Rajouri Garden, New Delhi, Delhi 110027</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Rajouri Garden</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>077018 99219</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://link.zomato.com/xqzv/rshare?id=6216205430563ff3</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Rajouri+House+Cafe+%26+Restro/@28.6441705,76.9696324,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d03dc42d7191d:0x65fb4ff7a30e4061!8m2!3d28.6441705!4d77.1220677!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11vj35knz1?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Spaced Out Cafe</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>4A , 2nd Floor, Shahpur Jat, New Delhi, Delhi 110017</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Shahpur Jat</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>092055 47663</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Cafe Punjab -Best Restaurant in Subhash Nagar-Best Cafe in West Delhi</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>4/13, Subash Nagar Marg, Block 17, Block 4, Subhash Nagar, New Delhi, Delhi, 110064</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Subhash Nagar</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>092682 04203</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/punjab-cafe-subhash-nagar-koramangala-delhi-1023178/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Friends Cafe</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Metro Station, A-10, Ramdutt Enclave, near Lal Mandir, Uttam Nagar East, New Delhi, Delhi 110059</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Uttam Nagar</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>089503 93361</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/friends-cafe-ram-datta-enclave-uttam-nagar-delhi-713664/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>BYTERRA - A Conscious Cafe</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>http://www.byterra.in/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
